--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/133.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/133.xlsx
@@ -426,13 +426,13 @@
         <v>-28.34893419976856</v>
       </c>
       <c r="E2">
-        <v>-6.314080556446427</v>
+        <v>-7.119406260074493</v>
       </c>
       <c r="F2">
-        <v>-1.311813553347259</v>
+        <v>-1.661352494090942</v>
       </c>
       <c r="G2">
-        <v>-10.48861057109996</v>
+        <v>-10.65712727068548</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-27.53657743305752</v>
       </c>
       <c r="E3">
-        <v>-6.252787660752609</v>
+        <v>-7.413933681059365</v>
       </c>
       <c r="F3">
-        <v>-0.9702572822703491</v>
+        <v>-2.01256699569316</v>
       </c>
       <c r="G3">
-        <v>-11.51847825127521</v>
+        <v>-9.969215770898161</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-26.46100353532948</v>
       </c>
       <c r="E4">
-        <v>-7.217470364710595</v>
+        <v>-8.203599921568907</v>
       </c>
       <c r="F4">
-        <v>-1.059590965548457</v>
+        <v>-1.604483198373427</v>
       </c>
       <c r="G4">
-        <v>-10.50612666754824</v>
+        <v>-9.833377466330788</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-25.22904357329043</v>
       </c>
       <c r="E5">
-        <v>-7.41112602717461</v>
+        <v>-8.610202545769614</v>
       </c>
       <c r="F5">
-        <v>-0.7748160945107555</v>
+        <v>-1.695863029694283</v>
       </c>
       <c r="G5">
-        <v>-10.0250845374189</v>
+        <v>-10.27074025861498</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.87463931030172</v>
       </c>
       <c r="E6">
-        <v>-8.823031767182105</v>
+        <v>-9.545377713093618</v>
       </c>
       <c r="F6">
-        <v>-0.6232974066099596</v>
+        <v>-1.838261947081021</v>
       </c>
       <c r="G6">
-        <v>-9.519206694653951</v>
+        <v>-9.50285922078103</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.45590651952725</v>
       </c>
       <c r="E7">
-        <v>-9.731747060879291</v>
+        <v>-9.041018920489332</v>
       </c>
       <c r="F7">
-        <v>-0.5994903474361161</v>
+        <v>-1.744266625440817</v>
       </c>
       <c r="G7">
-        <v>-9.360568662957615</v>
+        <v>-8.900157852629015</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.04198700861313</v>
       </c>
       <c r="E8">
-        <v>-10.5156666678731</v>
+        <v>-11.05234065099612</v>
       </c>
       <c r="F8">
-        <v>-0.4135648566694404</v>
+        <v>-1.78520067223718</v>
       </c>
       <c r="G8">
-        <v>-9.053197751818443</v>
+        <v>-8.153113388419236</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.71696811927059</v>
       </c>
       <c r="E9">
-        <v>-11.27948437874686</v>
+        <v>-11.08874052506978</v>
       </c>
       <c r="F9">
-        <v>-0.4452864861556925</v>
+        <v>-1.204884897348619</v>
       </c>
       <c r="G9">
-        <v>-8.79193611895024</v>
+        <v>-7.818476824218625</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.5286072759869</v>
       </c>
       <c r="E10">
-        <v>-10.99910843903596</v>
+        <v>-11.93278920993743</v>
       </c>
       <c r="F10">
-        <v>-0.3037308921689261</v>
+        <v>-1.367914751695786</v>
       </c>
       <c r="G10">
-        <v>-8.11012264404626</v>
+        <v>-7.204483185232155</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.54005449790679</v>
       </c>
       <c r="E11">
-        <v>-12.66888360293623</v>
+        <v>-13.90231765382743</v>
       </c>
       <c r="F11">
-        <v>0.07208410527077024</v>
+        <v>-1.382229077612486</v>
       </c>
       <c r="G11">
-        <v>-7.404142186705601</v>
+        <v>-7.113539188722837</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.7756918431912</v>
       </c>
       <c r="E12">
-        <v>-11.873493371281</v>
+        <v>-12.67464382187399</v>
       </c>
       <c r="F12">
-        <v>0.277387821618763</v>
+        <v>-1.054526274030882</v>
       </c>
       <c r="G12">
-        <v>-6.242478378066419</v>
+        <v>-6.268747556920537</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.21377993628029</v>
       </c>
       <c r="E13">
-        <v>-13.29760787721317</v>
+        <v>-13.73245459379972</v>
       </c>
       <c r="F13">
-        <v>0.2433476466723075</v>
+        <v>-0.8175001363436795</v>
       </c>
       <c r="G13">
-        <v>-6.299403208614187</v>
+        <v>-6.287647461404235</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.83900773986148</v>
       </c>
       <c r="E14">
-        <v>-14.50339106581353</v>
+        <v>-14.42625303956688</v>
       </c>
       <c r="F14">
-        <v>0.5629189122310873</v>
+        <v>-0.5531416101148652</v>
       </c>
       <c r="G14">
-        <v>-5.969921163818222</v>
+        <v>-4.424624716997218</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.59859145455535</v>
       </c>
       <c r="E15">
-        <v>-15.82451448738926</v>
+        <v>-14.41118227806935</v>
       </c>
       <c r="F15">
-        <v>0.9807432927837304</v>
+        <v>-0.08758987624158117</v>
       </c>
       <c r="G15">
-        <v>-4.970987221161916</v>
+        <v>-5.165230170133114</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.43303295783508</v>
       </c>
       <c r="E16">
-        <v>-16.91192789390313</v>
+        <v>-16.86165730394398</v>
       </c>
       <c r="F16">
-        <v>1.38248038864734</v>
+        <v>-0.05142595166252139</v>
       </c>
       <c r="G16">
-        <v>-4.831368273588693</v>
+        <v>-4.409300201695932</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.31180447924388</v>
       </c>
       <c r="E17">
-        <v>-17.38674745055538</v>
+        <v>-17.5534858635178</v>
       </c>
       <c r="F17">
-        <v>1.270255820067469</v>
+        <v>0.2943437690024154</v>
       </c>
       <c r="G17">
-        <v>-4.015060575606283</v>
+        <v>-3.007059048717914</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.19587232688813</v>
       </c>
       <c r="E18">
-        <v>-18.75342732064827</v>
+        <v>-18.66945582712404</v>
       </c>
       <c r="F18">
-        <v>1.470095751007196</v>
+        <v>0.5648589519775006</v>
       </c>
       <c r="G18">
-        <v>-3.431206143209338</v>
+        <v>-3.719309679309952</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.06657828469414</v>
       </c>
       <c r="E19">
-        <v>-20.00436845205312</v>
+        <v>-19.85117017637364</v>
       </c>
       <c r="F19">
-        <v>1.825514199961948</v>
+        <v>0.6727980123501917</v>
       </c>
       <c r="G19">
-        <v>-2.337898478865029</v>
+        <v>-2.896539796434884</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.92326575275938</v>
       </c>
       <c r="E20">
-        <v>-20.20769693499752</v>
+        <v>-20.71669741345967</v>
       </c>
       <c r="F20">
-        <v>1.940705049721436</v>
+        <v>0.9923423549084089</v>
       </c>
       <c r="G20">
-        <v>-2.81047885459599</v>
+        <v>-1.980746894451835</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.75216914387486</v>
       </c>
       <c r="E21">
-        <v>-21.0179315044499</v>
+        <v>-19.87129924333773</v>
       </c>
       <c r="F21">
-        <v>2.176415919645866</v>
+        <v>1.036104900469747</v>
       </c>
       <c r="G21">
-        <v>-3.162283907963261</v>
+        <v>-2.985298832888284</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.55902812145495</v>
       </c>
       <c r="E22">
-        <v>-22.39815604029974</v>
+        <v>-21.91897103470409</v>
       </c>
       <c r="F22">
-        <v>2.386416907739052</v>
+        <v>1.322934629932732</v>
       </c>
       <c r="G22">
-        <v>-2.251516414108826</v>
+        <v>-2.556480558640948</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.34791218803378</v>
       </c>
       <c r="E23">
-        <v>-22.06085265383841</v>
+        <v>-21.68508440915593</v>
       </c>
       <c r="F23">
-        <v>2.620666017103532</v>
+        <v>1.297348277162892</v>
       </c>
       <c r="G23">
-        <v>-1.866718463897178</v>
+        <v>-3.041650939057758</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.11301108424312</v>
       </c>
       <c r="E24">
-        <v>-23.15620900376173</v>
+        <v>-22.3828452696798</v>
       </c>
       <c r="F24">
-        <v>2.068796767868094</v>
+        <v>1.08474842766247</v>
       </c>
       <c r="G24">
-        <v>-1.568928271548656</v>
+        <v>-1.808197950399481</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.87099309641582</v>
       </c>
       <c r="E25">
-        <v>-23.32667435083247</v>
+        <v>-23.29932236782614</v>
       </c>
       <c r="F25">
-        <v>2.191347099016629</v>
+        <v>1.139221576329925</v>
       </c>
       <c r="G25">
-        <v>-1.779737190398367</v>
+        <v>-1.592770820522488</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.63225965156302</v>
       </c>
       <c r="E26">
-        <v>-22.83554323080458</v>
+        <v>-21.96795100957105</v>
       </c>
       <c r="F26">
-        <v>2.409128834272369</v>
+        <v>1.066239656628729</v>
       </c>
       <c r="G26">
-        <v>-1.599762692701428</v>
+        <v>-1.299840509025616</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.39829096128398</v>
       </c>
       <c r="E27">
-        <v>-24.07986373321022</v>
+        <v>-24.02995542117169</v>
       </c>
       <c r="F27">
-        <v>2.048297278498646</v>
+        <v>1.292262997468416</v>
       </c>
       <c r="G27">
-        <v>-1.604900659378377</v>
+        <v>-1.446368565139298</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.18974973601124</v>
       </c>
       <c r="E28">
-        <v>-24.13555037808255</v>
+        <v>-23.1548912178255</v>
       </c>
       <c r="F28">
-        <v>2.056778023675824</v>
+        <v>0.7905386286335373</v>
       </c>
       <c r="G28">
-        <v>-2.385461086627738</v>
+        <v>-2.735554587951205</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-13.01159620012281</v>
       </c>
       <c r="E29">
-        <v>-23.42702986331645</v>
+        <v>-23.48603135116239</v>
       </c>
       <c r="F29">
-        <v>1.749901744735207</v>
+        <v>0.8352751533328708</v>
       </c>
       <c r="G29">
-        <v>-2.017401254662646</v>
+        <v>-2.650903938512041</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.86565109411258</v>
       </c>
       <c r="E30">
-        <v>-23.14824341798224</v>
+        <v>-22.52329136255369</v>
       </c>
       <c r="F30">
-        <v>1.676818467855423</v>
+        <v>0.946962845607407</v>
       </c>
       <c r="G30">
-        <v>-2.09332861660583</v>
+        <v>-2.709626395287633</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.7632382106351</v>
       </c>
       <c r="E31">
-        <v>-22.28149802138814</v>
+        <v>-22.24956322268605</v>
       </c>
       <c r="F31">
-        <v>1.778243745797911</v>
+        <v>0.9897213216183566</v>
       </c>
       <c r="G31">
-        <v>-1.851691897694426</v>
+        <v>-1.955954218908233</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.69719719145831</v>
       </c>
       <c r="E32">
-        <v>-21.80141184946497</v>
+        <v>-20.03698252185636</v>
       </c>
       <c r="F32">
-        <v>1.671226402268006</v>
+        <v>0.9388875291445813</v>
       </c>
       <c r="G32">
-        <v>-2.142212132038709</v>
+        <v>-1.580809819489101</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.66402722030007</v>
       </c>
       <c r="E33">
-        <v>-22.39147201266441</v>
+        <v>-21.93182284393786</v>
       </c>
       <c r="F33">
-        <v>1.549710231082253</v>
+        <v>1.149737383608443</v>
       </c>
       <c r="G33">
-        <v>-1.925272082850268</v>
+        <v>-1.4874226403718</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.66239583939965</v>
       </c>
       <c r="E34">
-        <v>-22.06736007098743</v>
+        <v>-22.11931072480342</v>
       </c>
       <c r="F34">
-        <v>1.497702912525137</v>
+        <v>0.9108591018531339</v>
       </c>
       <c r="G34">
-        <v>-2.316899688509431</v>
+        <v>-2.843455198712671</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.67370247421269</v>
       </c>
       <c r="E35">
-        <v>-21.29837989974493</v>
+        <v>-20.99561971301411</v>
       </c>
       <c r="F35">
-        <v>1.966375338904794</v>
+        <v>1.019065808525534</v>
       </c>
       <c r="G35">
-        <v>-1.829087492752283</v>
+        <v>-3.18527233618796</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.6918085111837</v>
       </c>
       <c r="E36">
-        <v>-20.45841136995818</v>
+        <v>-20.73586644393414</v>
       </c>
       <c r="F36">
-        <v>1.955577631973328</v>
+        <v>1.047315954645143</v>
       </c>
       <c r="G36">
-        <v>-2.055455975636568</v>
+        <v>-2.292305645698185</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.70872954140223</v>
       </c>
       <c r="E37">
-        <v>-19.40625213359403</v>
+        <v>-18.20374303170121</v>
       </c>
       <c r="F37">
-        <v>1.707958877270709</v>
+        <v>0.9262258003506428</v>
       </c>
       <c r="G37">
-        <v>-1.827789758900888</v>
+        <v>-2.414948115746026</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.70748133179123</v>
       </c>
       <c r="E38">
-        <v>-18.26608653336481</v>
+        <v>-20.20394283004516</v>
       </c>
       <c r="F38">
-        <v>2.315337018842299</v>
+        <v>0.9320855122377688</v>
       </c>
       <c r="G38">
-        <v>-1.605503178666524</v>
+        <v>-2.607237842849054</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.69160465882319</v>
       </c>
       <c r="E39">
-        <v>-18.14726843235156</v>
+        <v>-18.27306944028464</v>
       </c>
       <c r="F39">
-        <v>1.77221932849558</v>
+        <v>1.029614873628276</v>
       </c>
       <c r="G39">
-        <v>-2.000540646231137</v>
+        <v>-1.779684221669739</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.65998474509031</v>
       </c>
       <c r="E40">
-        <v>-18.6242118433134</v>
+        <v>-18.77733313493476</v>
       </c>
       <c r="F40">
-        <v>1.938812521152486</v>
+        <v>1.44951232522423</v>
       </c>
       <c r="G40">
-        <v>-1.814805799295867</v>
+        <v>-2.698413577546122</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.60806346834329</v>
       </c>
       <c r="E41">
-        <v>-16.92555407219221</v>
+        <v>-18.47097281136785</v>
       </c>
       <c r="F41">
-        <v>2.204531450762663</v>
+        <v>1.192315317145032</v>
       </c>
       <c r="G41">
-        <v>-2.270810273511698</v>
+        <v>-2.497301246580936</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.55154816406722</v>
       </c>
       <c r="E42">
-        <v>-16.89034518678257</v>
+        <v>-18.21488760623409</v>
       </c>
       <c r="F42">
-        <v>1.712092349710006</v>
+        <v>1.057400993914661</v>
       </c>
       <c r="G42">
-        <v>-2.334154251860113</v>
+        <v>-2.792459555225737</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.49613459847985</v>
       </c>
       <c r="E43">
-        <v>-16.73640424136583</v>
+        <v>-17.09433029845808</v>
       </c>
       <c r="F43">
-        <v>2.00592997784881</v>
+        <v>0.9034267699919766</v>
       </c>
       <c r="G43">
-        <v>-2.462070420952012</v>
+        <v>-3.410157694670652</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.4480322170225</v>
       </c>
       <c r="E44">
-        <v>-15.33720087094984</v>
+        <v>-16.48520073121233</v>
       </c>
       <c r="F44">
-        <v>2.068804686397671</v>
+        <v>1.420606524855629</v>
       </c>
       <c r="G44">
-        <v>-1.588602843688545</v>
+        <v>-2.775916759165999</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.42414745627509</v>
       </c>
       <c r="E45">
-        <v>-13.83102588752468</v>
+        <v>-15.37000966513542</v>
       </c>
       <c r="F45">
-        <v>2.028475615261006</v>
+        <v>1.300059581690124</v>
       </c>
       <c r="G45">
-        <v>-2.274789549249902</v>
+        <v>-2.965432249107117</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.42391461921186</v>
       </c>
       <c r="E46">
-        <v>-13.92498266623582</v>
+        <v>-14.89307531112158</v>
       </c>
       <c r="F46">
-        <v>2.075491092772657</v>
+        <v>1.329375561890824</v>
       </c>
       <c r="G46">
-        <v>-2.270247480770021</v>
+        <v>-3.290819149071004</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.45043739497711</v>
       </c>
       <c r="E47">
-        <v>-13.28136876942166</v>
+        <v>-14.92145978620166</v>
       </c>
       <c r="F47">
-        <v>2.023296896917519</v>
+        <v>0.9772528049461019</v>
       </c>
       <c r="G47">
-        <v>-3.432864726524513</v>
+        <v>-3.4544527939861</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.51000549940587</v>
       </c>
       <c r="E48">
-        <v>-12.19283230135389</v>
+        <v>-15.22585475204925</v>
       </c>
       <c r="F48">
-        <v>2.229283190515066</v>
+        <v>0.9801937468310729</v>
       </c>
       <c r="G48">
-        <v>-3.191340566161444</v>
+        <v>-3.163452530538624</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.59366842369658</v>
       </c>
       <c r="E49">
-        <v>-11.96363717487768</v>
+        <v>-12.44863674109918</v>
       </c>
       <c r="F49">
-        <v>1.891070122625648</v>
+        <v>1.164489604210761</v>
       </c>
       <c r="G49">
-        <v>-2.678719142132997</v>
+        <v>-3.874322663640786</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.70759506840773</v>
       </c>
       <c r="E50">
-        <v>-11.43449404402942</v>
+        <v>-12.49340523513901</v>
       </c>
       <c r="F50">
-        <v>1.801443453753184</v>
+        <v>0.4190344786956672</v>
       </c>
       <c r="G50">
-        <v>-3.822866854323894</v>
+        <v>-4.398176768683981</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.85562794265374</v>
       </c>
       <c r="E51">
-        <v>-11.18984776423903</v>
+        <v>-11.70687269864277</v>
       </c>
       <c r="F51">
-        <v>1.90046624982195</v>
+        <v>0.9195742355057972</v>
       </c>
       <c r="G51">
-        <v>-2.080218856270316</v>
+        <v>-3.906799115381037</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.02972423561817</v>
       </c>
       <c r="E52">
-        <v>-11.01189684963362</v>
+        <v>-11.50901461229964</v>
       </c>
       <c r="F52">
-        <v>1.946154581776463</v>
+        <v>1.087652944311386</v>
       </c>
       <c r="G52">
-        <v>-3.137325705142695</v>
+        <v>-3.004900573026309</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.24004517452513</v>
       </c>
       <c r="E53">
-        <v>-10.60305715927312</v>
+        <v>-12.0021382608909</v>
       </c>
       <c r="F53">
-        <v>1.621015006218998</v>
+        <v>0.9831679465402682</v>
       </c>
       <c r="G53">
-        <v>-3.02678658958643</v>
+        <v>-2.638608572379187</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.48543740662324</v>
       </c>
       <c r="E54">
-        <v>-9.450918273767623</v>
+        <v>-10.34937657383744</v>
       </c>
       <c r="F54">
-        <v>1.749771880850141</v>
+        <v>1.253706093251127</v>
       </c>
       <c r="G54">
-        <v>-3.167418564094671</v>
+        <v>-4.789754716160055</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.75587998248977</v>
       </c>
       <c r="E55">
-        <v>-9.185681022664362</v>
+        <v>-10.27761384623788</v>
       </c>
       <c r="F55">
-        <v>1.819842949078759</v>
+        <v>0.8511011265458572</v>
       </c>
       <c r="G55">
-        <v>-4.463232299076198</v>
+        <v>-3.520465072039168</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.05648003736505</v>
       </c>
       <c r="E56">
-        <v>-9.087865984098682</v>
+        <v>-10.33988942079137</v>
       </c>
       <c r="F56">
-        <v>1.60314446866918</v>
+        <v>0.9081018698543538</v>
       </c>
       <c r="G56">
-        <v>-3.946158191297432</v>
+        <v>-4.051168695803113</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.37541528961568</v>
       </c>
       <c r="E57">
-        <v>-9.020708714564931</v>
+        <v>-9.473080625561161</v>
       </c>
       <c r="F57">
-        <v>2.2998071986355</v>
+        <v>0.7938454065849749</v>
       </c>
       <c r="G57">
-        <v>-4.416633060065418</v>
+        <v>-4.444521095688238</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.69769333163521</v>
       </c>
       <c r="E58">
-        <v>-7.72453265629746</v>
+        <v>-9.183534525984726</v>
       </c>
       <c r="F58">
-        <v>1.509837267249234</v>
+        <v>0.7030404605114233</v>
       </c>
       <c r="G58">
-        <v>-4.312913668320051</v>
+        <v>-5.353891539325101</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-15.01979672499026</v>
       </c>
       <c r="E59">
-        <v>-8.034275749948105</v>
+        <v>-9.53374859184192</v>
       </c>
       <c r="F59">
-        <v>1.709102312941656</v>
+        <v>0.7625070339302591</v>
       </c>
       <c r="G59">
-        <v>-4.131830137867456</v>
+        <v>-4.052853763482603</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-15.32254129897171</v>
       </c>
       <c r="E60">
-        <v>-7.452357783014448</v>
+        <v>-8.301614212990923</v>
       </c>
       <c r="F60">
-        <v>1.250172845353782</v>
+        <v>0.7795477095803875</v>
       </c>
       <c r="G60">
-        <v>-4.112423719916249</v>
+        <v>-5.770291957254631</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.59534344082533</v>
       </c>
       <c r="E61">
-        <v>-7.785956877737501</v>
+        <v>-7.42805799148929</v>
       </c>
       <c r="F61">
-        <v>1.652050891043865</v>
+        <v>0.6584543878740565</v>
       </c>
       <c r="G61">
-        <v>-4.477394812893201</v>
+        <v>-4.729449818616691</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.83503507700339</v>
       </c>
       <c r="E62">
-        <v>-7.170650471945291</v>
+        <v>-9.117740327127283</v>
       </c>
       <c r="F62">
-        <v>1.103483668642119</v>
+        <v>0.6369001503649256</v>
       </c>
       <c r="G62">
-        <v>-5.397044500429501</v>
+        <v>-5.249390858832466</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.02544804444346</v>
       </c>
       <c r="E63">
-        <v>-5.519147700665965</v>
+        <v>-8.595548403880791</v>
       </c>
       <c r="F63">
-        <v>1.445763693322385</v>
+        <v>0.6296151031539042</v>
       </c>
       <c r="G63">
-        <v>-4.693143065687504</v>
+        <v>-5.101833223056071</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.16676857548934</v>
       </c>
       <c r="E64">
-        <v>-6.678160809715108</v>
+        <v>-5.619915304284646</v>
       </c>
       <c r="F64">
-        <v>1.127994685095375</v>
+        <v>0.6096208159714812</v>
       </c>
       <c r="G64">
-        <v>-4.441498567610883</v>
+        <v>-5.099396661539168</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.25899364805199</v>
       </c>
       <c r="E65">
-        <v>-5.825666520823149</v>
+        <v>-7.635240205814216</v>
       </c>
       <c r="F65">
-        <v>1.269479804168904</v>
+        <v>0.4357045671615828</v>
       </c>
       <c r="G65">
-        <v>-4.636277824959443</v>
+        <v>-5.501293579461151</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.29081823851943</v>
       </c>
       <c r="E66">
-        <v>-5.521262498027547</v>
+        <v>-6.016002811839542</v>
       </c>
       <c r="F66">
-        <v>0.9467648823679771</v>
+        <v>0.4976179662197726</v>
       </c>
       <c r="G66">
-        <v>-5.339745578235795</v>
+        <v>-5.702041750417016</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.27111253061697</v>
       </c>
       <c r="E67">
-        <v>-6.384077179182988</v>
+        <v>-7.315964674377425</v>
       </c>
       <c r="F67">
-        <v>1.094378943334257</v>
+        <v>0.1062509766904609</v>
       </c>
       <c r="G67">
-        <v>-4.628928413862261</v>
+        <v>-5.482436712069462</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.20272375012305</v>
       </c>
       <c r="E68">
-        <v>-5.629275660058501</v>
+        <v>-5.797766592461891</v>
       </c>
       <c r="F68">
-        <v>0.8795270640220799</v>
+        <v>0.1339333642393847</v>
       </c>
       <c r="G68">
-        <v>-5.51238059647217</v>
+        <v>-6.85905755311906</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.08096186920482</v>
       </c>
       <c r="E69">
-        <v>-5.497053275982542</v>
+        <v>-7.604333370711865</v>
       </c>
       <c r="F69">
-        <v>1.090647732197482</v>
+        <v>0.3537335326843524</v>
       </c>
       <c r="G69">
-        <v>-5.872111095860455</v>
+        <v>-5.645067261686159</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.92016162153268</v>
       </c>
       <c r="E70">
-        <v>-5.36722645465664</v>
+        <v>-6.637467942282183</v>
       </c>
       <c r="F70">
-        <v>0.7269053249511803</v>
+        <v>0.2377927981739037</v>
       </c>
       <c r="G70">
-        <v>-5.869118362692954</v>
+        <v>-5.315283957246121</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.72346025123838</v>
       </c>
       <c r="E71">
-        <v>-6.425997263071992</v>
+        <v>-7.619549043377638</v>
       </c>
       <c r="F71">
-        <v>0.810056220335413</v>
+        <v>-0.004211719058482862</v>
       </c>
       <c r="G71">
-        <v>-5.375711344974437</v>
+        <v>-6.731267184757654</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.48989867040323</v>
       </c>
       <c r="E72">
-        <v>-6.408132433111733</v>
+        <v>-7.661387614734505</v>
       </c>
       <c r="F72">
-        <v>0.5521900965069427</v>
+        <v>-0.4537537698325895</v>
       </c>
       <c r="G72">
-        <v>-5.332505415141409</v>
+        <v>-5.594207350566336</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.23483399291533</v>
       </c>
       <c r="E73">
-        <v>-5.146979592819585</v>
+        <v>-7.314388765422756</v>
       </c>
       <c r="F73">
-        <v>0.8126630002722264</v>
+        <v>0.1325903816230921</v>
       </c>
       <c r="G73">
-        <v>-5.271518545216956</v>
+        <v>-6.219834246577805</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.95935222722994</v>
       </c>
       <c r="E74">
-        <v>-6.087765539439093</v>
+        <v>-7.649640753158607</v>
       </c>
       <c r="F74">
-        <v>0.7100341058340038</v>
+        <v>-0.1910462570206208</v>
       </c>
       <c r="G74">
-        <v>-5.439224161145355</v>
+        <v>-4.822042466804567</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.66829622491986</v>
       </c>
       <c r="E75">
-        <v>-6.740259773782292</v>
+        <v>-8.240239804764968</v>
       </c>
       <c r="F75">
-        <v>0.6757009452931921</v>
+        <v>0.01459478868736058</v>
       </c>
       <c r="G75">
-        <v>-4.712844122191707</v>
+        <v>-4.405228230682628</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.37694307941786</v>
       </c>
       <c r="E76">
-        <v>-6.750824703642187</v>
+        <v>-8.366552530260916</v>
       </c>
       <c r="F76">
-        <v>0.09226051863346879</v>
+        <v>-0.301824110246737</v>
       </c>
       <c r="G76">
-        <v>-4.704091039785873</v>
+        <v>-6.754940895908981</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.08494045735614</v>
       </c>
       <c r="E77">
-        <v>-7.850908780429517</v>
+        <v>-8.69878855430766</v>
       </c>
       <c r="F77">
-        <v>0.2071892650639518</v>
+        <v>-0.1164545002563805</v>
       </c>
       <c r="G77">
-        <v>-4.774436821949847</v>
+        <v>-5.451930034925078</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.80239482632969</v>
       </c>
       <c r="E78">
-        <v>-7.112604492114972</v>
+        <v>-9.522259853284462</v>
       </c>
       <c r="F78">
-        <v>0.4493822433002756</v>
+        <v>-0.07706931784531693</v>
       </c>
       <c r="G78">
-        <v>-4.894487134840438</v>
+        <v>-4.726301489808844</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.54117102640743</v>
       </c>
       <c r="E79">
-        <v>-7.315475599184596</v>
+        <v>-8.681045993145608</v>
       </c>
       <c r="F79">
-        <v>0.4633465702096629</v>
+        <v>-0.2638444668356258</v>
       </c>
       <c r="G79">
-        <v>-4.816808494306979</v>
+        <v>-4.974695032165901</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.2960939755746</v>
       </c>
       <c r="E80">
-        <v>-9.323772309054261</v>
+        <v>-9.925207998960978</v>
       </c>
       <c r="F80">
-        <v>0.2300350147471235</v>
+        <v>-0.3087409458324188</v>
       </c>
       <c r="G80">
-        <v>-4.350749893288381</v>
+        <v>-4.078371448499305</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.07813972931624</v>
       </c>
       <c r="E81">
-        <v>-9.073211842209862</v>
+        <v>-10.06096712123693</v>
       </c>
       <c r="F81">
-        <v>-0.02025386812892675</v>
+        <v>-0.5212798226550966</v>
       </c>
       <c r="G81">
-        <v>-4.510629379561944</v>
+        <v>-5.140897660419471</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.89050040896276</v>
       </c>
       <c r="E82">
-        <v>-9.611742499676028</v>
+        <v>-10.64552066004305</v>
       </c>
       <c r="F82">
-        <v>0.155856605226813</v>
+        <v>-0.8044796981598941</v>
       </c>
       <c r="G82">
-        <v>-4.243412075268592</v>
+        <v>-5.279288395597625</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.72486214714343</v>
       </c>
       <c r="E83">
-        <v>-10.71677167007973</v>
+        <v>-13.12892222042745</v>
       </c>
       <c r="F83">
-        <v>0.4275215586965072</v>
+        <v>-0.9472951302023925</v>
       </c>
       <c r="G83">
-        <v>-4.124169535489583</v>
+        <v>-5.106779178091743</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.59109067775419</v>
       </c>
       <c r="E84">
-        <v>-12.2404220347005</v>
+        <v>-11.36183920705035</v>
       </c>
       <c r="F84">
-        <v>0.2956511182356107</v>
+        <v>-0.5456981923122998</v>
       </c>
       <c r="G84">
-        <v>-3.87076382718607</v>
+        <v>-4.691828779108413</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.48829240445292</v>
       </c>
       <c r="E85">
-        <v>-13.35432248568523</v>
+        <v>-15.41736844630763</v>
       </c>
       <c r="F85">
-        <v>-0.03569737636333452</v>
+        <v>-0.1864368809537343</v>
       </c>
       <c r="G85">
-        <v>-3.449192337124198</v>
+        <v>-3.987977002549505</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.41078521926319</v>
       </c>
       <c r="E86">
-        <v>-14.27375667735858</v>
+        <v>-14.05682465849513</v>
       </c>
       <c r="F86">
-        <v>0.2351068329413183</v>
+        <v>-0.6619952606537224</v>
       </c>
       <c r="G86">
-        <v>-4.081443634759749</v>
+        <v>-3.520782884410938</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.37036785653944</v>
       </c>
       <c r="E87">
-        <v>-15.42984439219877</v>
+        <v>-17.05391819641363</v>
       </c>
       <c r="F87">
-        <v>-0.1495824605955429</v>
+        <v>-0.5268346711535005</v>
       </c>
       <c r="G87">
-        <v>-3.410041825576777</v>
+        <v>-4.155513780655403</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.36283663104181</v>
       </c>
       <c r="E88">
-        <v>-16.3871185126802</v>
+        <v>-18.04826240512186</v>
       </c>
       <c r="F88">
-        <v>0.3205580611677269</v>
+        <v>-0.3461385773196059</v>
       </c>
       <c r="G88">
-        <v>-2.745042611466756</v>
+        <v>-5.01576234958056</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.38477374862292</v>
       </c>
       <c r="E89">
-        <v>-19.25341613583516</v>
+        <v>-19.63674240363644</v>
       </c>
       <c r="F89">
-        <v>0.01041459692355816</v>
+        <v>0.08546879581510673</v>
       </c>
       <c r="G89">
-        <v>-3.444130512994652</v>
+        <v>-4.377201152147158</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.43857097106678</v>
       </c>
       <c r="E90">
-        <v>-19.8897029617049</v>
+        <v>-19.88718513015664</v>
       </c>
       <c r="F90">
-        <v>0.2164127683154711</v>
+        <v>-0.8937777480549051</v>
       </c>
       <c r="G90">
-        <v>-2.666337701816123</v>
+        <v>-3.276550697796745</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.50896519196147</v>
       </c>
       <c r="E91">
-        <v>-22.18922130653384</v>
+        <v>-22.92308316184686</v>
       </c>
       <c r="F91">
-        <v>0.2130656058631898</v>
+        <v>-0.6208870062066607</v>
       </c>
       <c r="G91">
-        <v>-3.362264032354016</v>
+        <v>-4.311367643553211</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.58712763151217</v>
       </c>
       <c r="E92">
-        <v>-23.8706165347378</v>
+        <v>-24.43140011347766</v>
       </c>
       <c r="F92">
-        <v>-0.1211446453249545</v>
+        <v>-0.8237320191209337</v>
       </c>
       <c r="G92">
-        <v>-2.8123426917346</v>
+        <v>-3.173867506805171</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.66343813885548</v>
       </c>
       <c r="E93">
-        <v>-26.98258387280887</v>
+        <v>-27.03879129219207</v>
       </c>
       <c r="F93">
-        <v>0.1111667998519849</v>
+        <v>-0.84781939424181</v>
       </c>
       <c r="G93">
-        <v>-2.895069914215448</v>
+        <v>-4.278318467434667</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.71401800042745</v>
       </c>
       <c r="E94">
-        <v>-29.15136970151037</v>
+        <v>-29.03306784653399</v>
       </c>
       <c r="F94">
-        <v>-0.0575208438780901</v>
+        <v>-0.7295830780069318</v>
       </c>
       <c r="G94">
-        <v>-3.220969948737921</v>
+        <v>-4.161932928456049</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.73279930661335</v>
       </c>
       <c r="E95">
-        <v>-31.98129009296171</v>
+        <v>-31.355654237958</v>
       </c>
       <c r="F95">
-        <v>0.1586257150199588</v>
+        <v>-0.9090541753152339</v>
       </c>
       <c r="G95">
-        <v>-3.15402078629724</v>
+        <v>-3.646775626544521</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.715159947958</v>
       </c>
       <c r="E96">
-        <v>-33.46377210037874</v>
+        <v>-33.22186781160001</v>
       </c>
       <c r="F96">
-        <v>-0.121640345276487</v>
+        <v>-0.5957504259168058</v>
       </c>
       <c r="G96">
-        <v>-3.809935863447501</v>
+        <v>-4.606883491116254</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.65106636051361</v>
       </c>
       <c r="E97">
-        <v>-35.84572678604331</v>
+        <v>-35.94605512768325</v>
       </c>
       <c r="F97">
-        <v>-0.4580582825107539</v>
+        <v>-0.8418314021755334</v>
       </c>
       <c r="G97">
-        <v>-3.657094596990429</v>
+        <v>-4.642355986569545</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.56018281535412</v>
       </c>
       <c r="E98">
-        <v>-39.92448030424893</v>
+        <v>-37.35412072173224</v>
       </c>
       <c r="F98">
-        <v>-0.2400255298674166</v>
+        <v>-0.771754790976211</v>
       </c>
       <c r="G98">
-        <v>-3.826101257315762</v>
+        <v>-4.049844477587405</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.44831515624799</v>
       </c>
       <c r="E99">
-        <v>-42.40264921291747</v>
+        <v>-41.79284490304458</v>
       </c>
       <c r="F99">
-        <v>-0.00527676128661589</v>
+        <v>-1.369059771072649</v>
       </c>
       <c r="G99">
-        <v>-4.371576535275937</v>
+        <v>-4.947558490380494</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.33758391522904</v>
       </c>
       <c r="E100">
-        <v>-44.01723586408627</v>
+        <v>-43.79703428698929</v>
       </c>
       <c r="F100">
-        <v>-0.1234410189023417</v>
+        <v>-1.576885539090979</v>
       </c>
       <c r="G100">
-        <v>-4.677040572184489</v>
+        <v>-3.946456140395966</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.24056105671604</v>
       </c>
       <c r="E101">
-        <v>-46.6850957562251</v>
+        <v>-46.5036647093448</v>
       </c>
       <c r="F101">
-        <v>-0.1844144884997181</v>
+        <v>-1.757469981657835</v>
       </c>
       <c r="G101">
-        <v>-4.697483190889488</v>
+        <v>-5.272938769253303</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.20520724806475</v>
       </c>
       <c r="E102">
-        <v>-49.87132440742946</v>
+        <v>-49.53375044464617</v>
       </c>
       <c r="F102">
-        <v>-0.6634918627438127</v>
+        <v>-1.37622683219297</v>
       </c>
       <c r="G102">
-        <v>-4.821155240600042</v>
+        <v>-5.938153168823376</v>
       </c>
     </row>
   </sheetData>
